--- a/templates/09_بنود_المستخلص.xlsx
+++ b/templates/09_بنود_المستخلص.xlsx
@@ -227,36 +227,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>المنظومة</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
-      <text>
-        <t>زي مقايسة العقد</t>
-      </text>
-    </comment>
-    <comment ref="B1" authorId="0" shapeId="0">
-      <text>
-        <t>للمراجعة بس — السيستم بيجيب الوصف من العقد</t>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
-      <text>
-        <t>كمية المستخلص ده بس، مش التراكمي</t>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
-      <text>
-        <t>اختياري</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -680,7 +650,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -690,7 +659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -797,6 +766,44 @@
       <c r="A16" s="10" t="inlineStr">
         <is>
           <t>• نسخة القالب: 1.0 — لو القالب قديم السيستم هيطلب تنزيل النسخة الجديدة.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>شرح الأعمدة</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>• [بنود المستخلص] رقم البند: زي مقايسة العقد</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>• [بنود المستخلص] وصف البند (اختياري): للمراجعة بس — السيستم بيجيب الوصف من العقد</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>• [بنود المستخلص] الكمية المطلوب فوترتها: كمية المستخلص ده بس، مش التراكمي</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>• [بنود المستخلص] كود الموقع: اختياري</t>
         </is>
       </c>
     </row>
@@ -811,7 +818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -838,6 +845,18 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>examples</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>{"بنود المستخلص": [["1-1-1-2", "غرفة تفتيش طراز HH-I", "عدد", "2", "#75", ""], ["1-9-1", "حفر ضيق Micro trenching", "م.ط", "1292", "#75", ""]]}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/templates/09_بنود_المستخلص.xlsx
+++ b/templates/09_بنود_المستخلص.xlsx
@@ -645,7 +645,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="D3:D5000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" error="لازم رقم موجب" type="decimal" operator="greaterThanOrEqual">
+    <dataValidation sqref="D3:D5000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" error="يجب إدخال رقم موجب" type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
@@ -668,7 +668,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>قالب بنود المستخلص</t>
+          <t>نموذج بنود المستخلص</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>مين بيرفعه: الشركة المنفذة.</t>
+          <t>الجهة المسؤولة عن الرفع: المقاول (الشركة المنفذة).</t>
         </is>
       </c>
     </row>
@@ -692,28 +692,28 @@
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>قواعد الملء</t>
+          <t>قواعد تعبئة البيانات</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>• مفيش عمود سعر — السعر بيتجاب من العقد والإجمالي بيتحسب أوتوماتيك.</t>
+          <t>• لا يتضمن النموذج عمود سعر — يُستمد السعر من العقد ويُحتسب الإجمالي تلقائياً.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>• السيستم بيضيف الكميات السابقة ويقارن التراكمي بأمر التكليف ويقترح فئة التجاوز.</t>
+          <t>• تضيف المنظومة الكميات السابقة وتقارن الكمية التراكمية بأمر التكليف وتقترح فئة التجاوز.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>• بند مش موجود في العقد؟ اكتبه بكود يبدأ بـ N (مثلاً N-1) مع الوصف والوحدة — هيتصنّف C5 ويروح للتسعير.</t>
+          <t>• في حال وجود بند غير مدرج في العقد، يُكتب بكود يبدأ بـ N (مثال: N-1) مع الوصف والوحدة — ويُصنَّف ضمن الفئة C5 ويُحال إلى مرحلة التسعير.</t>
         </is>
       </c>
     </row>
@@ -723,49 +723,49 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>قواعد عامة لكل القوالب</t>
+          <t>قواعد عامة لجميع النماذج</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>• ما تغيّرش أسماء الشيتات ولا ترتيب الأعمدة ولا الصف التاني (اسم العمود التقني).</t>
+          <t>• لا يجوز تغيير أسماء أوراق العمل أو ترتيب الأعمدة أو الصف الثاني (الاسم التقني للعمود).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>• العمود اللي عليه * إلزامي. الأعمدة اللي فيها قائمة لازم تختار منها.</t>
+          <t>• العمود المميز بعلامة * إلزامي، ويجب الاختيار من القائمة في الأعمدة التي تتضمن قائمة اختيار.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>• الصفوف الرمادي أمثلة — امسحها قبل الرفع.</t>
+          <t>• الصفوف الرمادية أمثلة توضيحية — يرجى حذفها قبل الرفع.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>• الأرقام من غير فواصل أو عملة. التواريخ يوم/شهر/سنة.</t>
+          <t>• تُدخل الأرقام دون فواصل أو رمز عملة، والتواريخ بصيغة يوم/شهر/سنة.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>• عند الرفع السيستم بيعرض معاينة بكل صف وأخطاؤه قبل الحفظ — مفيش حاجة بتتحفظ قبل ما توافق.</t>
+          <t>• عند الرفع تعرض المنظومة نتيجة المراجعة لكل صف وأخطاءه قبل الحفظ — ولا يُحفظ أي سجل قبل «اعتماد الاستيراد».</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>• نسخة القالب: 1.0 — لو القالب قديم السيستم هيطلب تنزيل النسخة الجديدة.</t>
+          <t>• إصدار النموذج: 1.0 — إذا كان النموذج قديماً ستطلب المنظومة تحميل الإصدار الأحدث.</t>
         </is>
       </c>
     </row>
@@ -775,28 +775,28 @@
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>شرح الأعمدة</t>
+          <t>إيضاح الأعمدة</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>• [بنود المستخلص] رقم البند: زي مقايسة العقد</t>
+          <t>• [بنود المستخلص] رقم البند: وفق جدول كميات العقد</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>• [بنود المستخلص] وصف البند (اختياري): للمراجعة بس — السيستم بيجيب الوصف من العقد</t>
+          <t>• [بنود المستخلص] وصف البند (اختياري): للمراجعة فقط — تستمد المنظومة الوصف من العقد</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>• [بنود المستخلص] الكمية المطلوب فوترتها: كمية المستخلص ده بس، مش التراكمي</t>
+          <t>• [بنود المستخلص] الكمية المطلوب فوترتها: كمية هذا المستخلص فقط، وليست الكمية التراكمية</t>
         </is>
       </c>
     </row>

--- a/templates/09_بنود_المستخلص.xlsx
+++ b/templates/09_بنود_المستخلص.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>غرفة تفتيش طراز HH-I</t>
+          <t>مثال — غرفة تفتيش طراز HH-I</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>حفر ضيق Micro trenching</t>
+          <t>مثال — حفر ضيق Micro trenching</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{"بنود المستخلص": [["1-1-1-2", "غرفة تفتيش طراز HH-I", "عدد", "2", "#75", ""], ["1-9-1", "حفر ضيق Micro trenching", "م.ط", "1292", "#75", ""]]}</t>
+          <t>{"بنود المستخلص": [["1-1-1-2", "مثال — غرفة تفتيش طراز HH-I", "عدد", "2", "#75", ""], ["1-9-1", "مثال — حفر ضيق Micro trenching", "م.ط", "1292", "#75", ""]]}</t>
         </is>
       </c>
     </row>
